--- a/SGC-CKN/Excel/d395e2af-dcd7-455d-b39f-ea65c5684c1e_Cọc_khoan_nhồi_-_Trụ_HN_P479_C9_D2000_04-03-2026.xlsx
+++ b/SGC-CKN/Excel/d395e2af-dcd7-455d-b39f-ea65c5684c1e_Cọc_khoan_nhồi_-_Trụ_HN_P479_C9_D2000_04-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="80">
   <si>
     <t>Dự án</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Biên bản số</t>
   </si>
   <si>
-    <t/>
+    <t>ĐSTĐC/CKN09-HN479/06</t>
   </si>
   <si>
     <t>Đường kính</t>
@@ -106,6 +106,9 @@
 03/03/2026</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
@@ -179,23 +182,27 @@
     <t>5</t>
   </si>
   <si>
-    <t>Cát, san, sỏi đa khoáng, đa sắc kết cấu chặt</t>
+    <t>Cát, sạn, sỏi đa khoáng, đa sắc kết cấu chặt</t>
   </si>
   <si>
     <t xml:space="preserve">17h20
 03/03/2026</t>
   </si>
   <si>
+    <t xml:space="preserve">18h02
+03/03/2026</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Cuội sỏi to, sạn cát đa khoáng, đa sắc, kết cấu rất chặt</t>
+  </si>
+  <si>
     <t xml:space="preserve">09h08
 04/03/2026</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>Cuội sỏi to, sạn cát đa khoáng, đa sắc, kết cấu rất chặt</t>
-  </si>
-  <si>
     <t xml:space="preserve">09h51
 04/03/2026</t>
   </si>
@@ -244,7 +251,7 @@
 04/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">16h30
+    <t xml:space="preserve">16h35
 04/03/2026</t>
   </si>
   <si>
@@ -282,7 +289,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -338,12 +345,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <color rgb="FF365314"/>
       <sz val="10"/>
       <name val="Arial"/>
@@ -361,7 +362,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -416,11 +417,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDD6FE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
@@ -521,7 +517,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -589,22 +585,19 @@
     <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1205,24 +1198,24 @@
         <v>4.64</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>29</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F12" s="9">
         <v>-8.81</v>
@@ -1240,24 +1233,24 @@
         <v>4.28</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F13" s="9">
         <v>-10.88</v>
@@ -1275,24 +1268,24 @@
         <v>4.12</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F14" s="9">
         <v>-12.94</v>
@@ -1310,24 +1303,24 @@
         <v>2.11</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>35</v>
-      </c>
       <c r="E15" s="14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F15" s="12">
         <v>-14.1</v>
@@ -1345,24 +1338,24 @@
         <v>4.71</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F16" s="12">
         <v>-16.14</v>
@@ -1380,24 +1373,24 @@
         <v>5.94</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F17" s="12">
         <v>-18.22</v>
@@ -1415,24 +1408,24 @@
         <v>6.98</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F18" s="12">
         <v>-20.43</v>
@@ -1450,24 +1443,24 @@
         <v>7.99</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F19" s="12">
         <v>-22.56</v>
@@ -1485,24 +1478,24 @@
         <v>5.28</v>
       </c>
       <c r="K19" s="13" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F20" s="12">
         <v>-24.67</v>
@@ -1520,24 +1513,24 @@
         <v>7.72</v>
       </c>
       <c r="K20" s="13" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F21" s="12">
         <v>-26.73</v>
@@ -1555,24 +1548,24 @@
         <v>8.03</v>
       </c>
       <c r="K21" s="13" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F22" s="12">
         <v>-28.87</v>
@@ -1590,24 +1583,24 @@
         <v>7.55</v>
       </c>
       <c r="K22" s="13" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>45</v>
-      </c>
       <c r="E23" s="18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F23" s="16">
         <v>-31.01</v>
@@ -1625,24 +1618,24 @@
         <v>5.27</v>
       </c>
       <c r="K23" s="17" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="D24" s="21" t="s">
-        <v>48</v>
-      </c>
       <c r="E24" s="21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F24" s="19">
         <v>-33.12</v>
@@ -1660,24 +1653,24 @@
         <v>5.11</v>
       </c>
       <c r="K24" s="20" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B25" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F25" s="19">
         <v>-35.08</v>
@@ -1686,452 +1679,452 @@
         <v>-37.06</v>
       </c>
       <c r="H25" s="19">
-        <v>15.8</v>
+        <v>0.7</v>
       </c>
       <c r="I25" s="19">
         <v>1.98</v>
       </c>
-      <c r="J25" s="22">
-        <v>0.13</v>
+      <c r="J25" s="8">
+        <v>2.83</v>
       </c>
       <c r="K25" s="20" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="B26" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="24" t="s">
+      <c r="A26" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="D26" s="25" t="s">
-        <v>52</v>
-      </c>
-      <c r="E26" s="25" t="s">
+      <c r="B26" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="F26" s="23">
+      <c r="D26" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="E26" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="F26" s="22">
         <v>-37.06</v>
       </c>
-      <c r="G26" s="23">
+      <c r="G26" s="22">
         <v>-39.12</v>
       </c>
-      <c r="H26" s="23">
+      <c r="H26" s="22">
         <v>0.72</v>
       </c>
-      <c r="I26" s="23">
+      <c r="I26" s="22">
         <v>2.06</v>
       </c>
       <c r="J26" s="8">
         <v>2.87</v>
       </c>
-      <c r="K26" s="24" t="s">
-        <v>9</v>
+      <c r="K26" s="23" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="B27" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="24" t="s">
+      <c r="A27" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="D27" s="25" t="s">
+      <c r="B27" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="E27" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="F27" s="23">
+      <c r="D27" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="E27" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F27" s="22">
         <v>-39.12</v>
       </c>
-      <c r="G27" s="23">
+      <c r="G27" s="22">
         <v>-40.98</v>
       </c>
-      <c r="H27" s="23">
+      <c r="H27" s="22">
         <v>0.62</v>
       </c>
-      <c r="I27" s="23">
+      <c r="I27" s="22">
         <v>1.86</v>
       </c>
       <c r="J27" s="8">
         <v>3.02</v>
       </c>
-      <c r="K27" s="24" t="s">
-        <v>9</v>
+      <c r="K27" s="23" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="B28" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="24" t="s">
+      <c r="A28" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="D28" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="E28" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="F28" s="23">
+      <c r="B28" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="E28" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="F28" s="22">
         <v>-40.98</v>
       </c>
-      <c r="G28" s="23">
+      <c r="G28" s="22">
         <v>-43.1</v>
       </c>
-      <c r="H28" s="23">
+      <c r="H28" s="22">
         <v>0.57</v>
       </c>
-      <c r="I28" s="23">
+      <c r="I28" s="22">
         <v>2.12</v>
       </c>
       <c r="J28" s="8">
         <v>3.74</v>
       </c>
-      <c r="K28" s="24" t="s">
-        <v>9</v>
+      <c r="K28" s="23" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="B29" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="24" t="s">
+      <c r="A29" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="E29" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="F29" s="23">
+      <c r="B29" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="E29" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="F29" s="22">
         <v>-43.1</v>
       </c>
-      <c r="G29" s="23">
+      <c r="G29" s="22">
         <v>-45.07</v>
       </c>
-      <c r="H29" s="23">
+      <c r="H29" s="22">
         <v>0.63</v>
       </c>
-      <c r="I29" s="23">
+      <c r="I29" s="22">
         <v>1.97</v>
       </c>
       <c r="J29" s="8">
         <v>3.11</v>
       </c>
-      <c r="K29" s="24" t="s">
-        <v>9</v>
+      <c r="K29" s="23" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="30" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="B30" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="24" t="s">
+      <c r="A30" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="25" t="s">
-        <v>59</v>
-      </c>
-      <c r="E30" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="F30" s="23">
+      <c r="B30" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="D30" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="E30" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="F30" s="22">
         <v>-45.07</v>
       </c>
-      <c r="G30" s="23">
+      <c r="G30" s="22">
         <v>-49.11</v>
       </c>
-      <c r="H30" s="23">
+      <c r="H30" s="22">
         <v>0.62</v>
       </c>
-      <c r="I30" s="23">
+      <c r="I30" s="22">
         <v>4.04</v>
       </c>
       <c r="J30" s="15">
         <v>6.55</v>
       </c>
-      <c r="K30" s="24" t="s">
-        <v>9</v>
+      <c r="K30" s="23" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="31" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="B31" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="24" t="s">
+      <c r="A31" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="D31" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="E31" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="F31" s="23">
+      <c r="B31" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="E31" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="F31" s="22">
         <v>-49.11</v>
       </c>
-      <c r="G31" s="23">
+      <c r="G31" s="22">
         <v>-51.23</v>
       </c>
-      <c r="H31" s="23">
+      <c r="H31" s="22">
         <v>0.43</v>
       </c>
-      <c r="I31" s="23">
+      <c r="I31" s="22">
         <v>2.12</v>
       </c>
       <c r="J31" s="8">
         <v>4.89</v>
       </c>
-      <c r="K31" s="24" t="s">
-        <v>9</v>
+      <c r="K31" s="23" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="32" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="B32" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="24" t="s">
+      <c r="A32" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="D32" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="E32" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="F32" s="23">
+      <c r="B32" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="E32" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="F32" s="22">
         <v>-51.23</v>
       </c>
-      <c r="G32" s="23">
+      <c r="G32" s="22">
         <v>-53.2</v>
       </c>
-      <c r="H32" s="23">
+      <c r="H32" s="22">
         <v>0.3</v>
       </c>
-      <c r="I32" s="23">
+      <c r="I32" s="22">
         <v>1.97</v>
       </c>
       <c r="J32" s="15">
         <v>6.57</v>
       </c>
-      <c r="K32" s="24" t="s">
-        <v>9</v>
+      <c r="K32" s="23" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="B33" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="24" t="s">
+      <c r="A33" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="D33" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="E33" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="F33" s="23">
+      <c r="B33" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="D33" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="E33" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="F33" s="22">
         <v>-53.2</v>
       </c>
-      <c r="G33" s="23">
+      <c r="G33" s="22">
         <v>-55.19</v>
       </c>
-      <c r="H33" s="23">
+      <c r="H33" s="22">
         <v>0.75</v>
       </c>
-      <c r="I33" s="23">
+      <c r="I33" s="22">
         <v>1.99</v>
       </c>
       <c r="J33" s="8">
         <v>2.65</v>
       </c>
-      <c r="K33" s="24" t="s">
-        <v>9</v>
+      <c r="K33" s="23" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="B34" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="24" t="s">
+      <c r="A34" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="D34" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="E34" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="F34" s="23">
+      <c r="B34" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="D34" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="E34" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="F34" s="22">
         <v>-55.19</v>
       </c>
-      <c r="G34" s="23">
+      <c r="G34" s="22">
         <v>-57.22</v>
       </c>
-      <c r="H34" s="23">
+      <c r="H34" s="22">
         <v>0.67</v>
       </c>
-      <c r="I34" s="23">
+      <c r="I34" s="22">
         <v>2.03</v>
       </c>
       <c r="J34" s="8">
         <v>3.05</v>
       </c>
-      <c r="K34" s="24" t="s">
-        <v>9</v>
+      <c r="K34" s="23" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="35" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="B35" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="24" t="s">
+      <c r="A35" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="D35" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="E35" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="F35" s="23">
+      <c r="B35" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="D35" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="E35" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="F35" s="22">
         <v>-57.22</v>
       </c>
-      <c r="G35" s="23">
+      <c r="G35" s="22">
         <v>-59.35</v>
       </c>
-      <c r="H35" s="23">
+      <c r="H35" s="22">
         <v>0.62</v>
       </c>
-      <c r="I35" s="23">
+      <c r="I35" s="22">
         <v>2.13</v>
       </c>
       <c r="J35" s="8">
         <v>3.45</v>
       </c>
-      <c r="K35" s="24" t="s">
-        <v>9</v>
+      <c r="K35" s="23" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="B36" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="24" t="s">
+      <c r="A36" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="D36" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="E36" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="F36" s="23">
+      <c r="B36" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="D36" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="E36" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="F36" s="22">
         <v>-59.35</v>
       </c>
-      <c r="G36" s="23">
+      <c r="G36" s="22">
         <v>-61.2</v>
       </c>
-      <c r="H36" s="23">
+      <c r="H36" s="22">
         <v>0.47</v>
       </c>
-      <c r="I36" s="23">
+      <c r="I36" s="22">
         <v>1.85</v>
       </c>
       <c r="J36" s="8">
         <v>3.96</v>
       </c>
-      <c r="K36" s="24" t="s">
-        <v>9</v>
+      <c r="K36" s="23" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="B37" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C37" s="24" t="s">
+      <c r="A37" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="D37" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="E37" s="25" t="s">
-        <v>67</v>
-      </c>
-      <c r="F37" s="23">
+      <c r="B37" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="D37" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="E37" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="F37" s="22">
         <v>-61.2</v>
       </c>
-      <c r="G37" s="23">
+      <c r="G37" s="22">
         <v>-63</v>
       </c>
-      <c r="H37" s="23">
-        <v>0.5</v>
-      </c>
-      <c r="I37" s="23">
+      <c r="H37" s="22">
+        <v>0.58</v>
+      </c>
+      <c r="I37" s="22">
         <v>1.8</v>
       </c>
       <c r="J37" s="8">
-        <v>3.6</v>
-      </c>
-      <c r="K37" s="24" t="s">
-        <v>9</v>
+        <v>3.09</v>
+      </c>
+      <c r="K37" s="23" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="40" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="B40" s="26"/>
-      <c r="C40" s="26"/>
-      <c r="D40" s="26"/>
-      <c r="E40" s="26"/>
-      <c r="F40" s="26"/>
-      <c r="G40" s="26"/>
-      <c r="H40" s="26"/>
-      <c r="I40" s="26"/>
-      <c r="J40" s="26"/>
-      <c r="K40" s="26"/>
+      <c r="A40" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="B40" s="25"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="25"/>
+      <c r="H40" s="25"/>
+      <c r="I40" s="25"/>
+      <c r="J40" s="25"/>
+      <c r="K40" s="25"/>
     </row>
     <row r="41" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="42" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2226,31 +2219,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2290,7 +2283,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="9">
         <v>3</v>
@@ -2319,7 +2312,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4" s="12">
         <v>8</v>
@@ -2348,7 +2341,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
@@ -2377,7 +2370,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D6" s="19">
         <v>2</v>
@@ -2389,71 +2382,71 @@
         <v>-37.06</v>
       </c>
       <c r="G6" s="19">
-        <v>16.18</v>
+        <v>1.08</v>
       </c>
       <c r="H6" s="19">
         <v>3.94</v>
       </c>
-      <c r="I6" s="22">
-        <v>0.24</v>
+      <c r="I6" s="8">
+        <v>3.64</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="23">
+      <c r="A7" s="22">
         <v>6</v>
       </c>
-      <c r="B7" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="D7" s="23">
+      <c r="B7" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="22">
         <v>12</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="22">
         <v>-37.06</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="22">
         <v>-63</v>
       </c>
-      <c r="G7" s="23">
-        <v>6.88</v>
-      </c>
-      <c r="H7" s="23">
+      <c r="G7" s="22">
+        <v>6.97</v>
+      </c>
+      <c r="H7" s="22">
         <v>25.94</v>
       </c>
       <c r="I7" s="8">
-        <v>3.77</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="B8" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="28">
+      <c r="A8" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="27">
         <v>27</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="27">
         <v>-6.72</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="27">
         <v>-63</v>
       </c>
-      <c r="G8" s="28">
-        <v>28.03</v>
-      </c>
-      <c r="H8" s="28">
+      <c r="G8" s="27">
+        <v>13.02</v>
+      </c>
+      <c r="H8" s="27">
         <v>56.28</v>
       </c>
-      <c r="I8" s="28">
-        <v>2.01</v>
+      <c r="I8" s="27">
+        <v>4.32</v>
       </c>
     </row>
   </sheetData>
